--- a/output/pdf_financials_xlsx/BEEP.xlsx
+++ b/output/pdf_financials_xlsx/BEEP.xlsx
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>7.288786</v>
+        <v>-7.288786</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>18.144899</v>
+        <v>-18.144899</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-8.130546000000001</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>7.288786</v>
+        <v>-7.288786</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>18.144899</v>
+        <v>-18.144899</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-8.130546000000001</v>
@@ -1145,10 +1145,10 @@
         <v>-0.028803</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>7.288786</v>
+        <v>-7.288786</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>18.144899</v>
+        <v>-18.144899</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-8.130546000000001</v>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>60.739883</v>
+        <v>-60.739883</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>86.404281</v>
+        <v>-86.404281</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>-101.631825</v>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>7.288786</v>
+        <v>-7.288786</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>18.144899</v>
+        <v>-18.144899</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-8.130546000000001</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>7.288786</v>
+        <v>-7.288786</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>18.144899</v>
+        <v>-18.144899</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-8.130546000000001</v>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -3176,19 +3176,19 @@
         <v>0.046924</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>6.175045</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>7.706056</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>11.783804</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>13.148157</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>13.716389</v>
       </c>
     </row>
     <row r="93">
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>18.144899</v>
+        <v>-18.144899</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>-8.130546000000001</v>
@@ -5414,7 +5414,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -5859,7 +5863,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -14035,7 +14043,7 @@
         </is>
       </c>
       <c r="H189" s="5" t="n">
-        <v>18.144899</v>
+        <v>-18.144899</v>
       </c>
       <c r="I189" s="5" t="n">
         <v>-9.449716</v>
@@ -14130,13 +14138,13 @@
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>6.992332</v>
+        <v>-6.992332</v>
       </c>
       <c r="H191" s="5" t="n">
-        <v>18.102899</v>
+        <v>-18.102899</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>8.130546000000001</v>
+        <v>-8.130546000000001</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -14738,10 +14746,10 @@
         </is>
       </c>
       <c r="G203" s="5" t="n">
-        <v>7.288786</v>
+        <v>-7.288786</v>
       </c>
       <c r="H203" s="5" t="n">
-        <v>18.144899</v>
+        <v>-18.144899</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BEEP.xlsx
+++ b/output/pdf_financials_xlsx/BEEP.xlsx
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>7.288786</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>18.144899</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>9.449716</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>12.805086</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>19.953388</v>
       </c>
     </row>
     <row r="11">
@@ -743,16 +743,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-7.288786</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-18.144899</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-9.449716</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>-12.805086</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.029203</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.151278</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.43908</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.67132</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.242123</v>
       </c>
     </row>
     <row r="13">
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7.288786</v>
+        <v>-7.259583</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-18.144899</v>
+        <v>-17.993621</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-8.130546000000001</v>
+        <v>-7.691466</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-8.130546000000001</v>
+        <v>-7.459226</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-17.770769</v>
+        <v>-17.528646</v>
       </c>
     </row>
     <row r="28">
@@ -1337,19 +1337,19 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.288786</v>
+        <v>-7.259583</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-18.144899</v>
+        <v>-17.993621</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-8.130546000000001</v>
+        <v>-7.691466</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-8.130546000000001</v>
+        <v>-7.459226</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-17.770769</v>
+        <v>-17.528646</v>
       </c>
     </row>
     <row r="30">
@@ -1482,25 +1482,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.247482</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.220265</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>20.197903</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>7.043611</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>15.945841</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>9.454159000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>7.371084</v>
       </c>
     </row>
     <row r="35">
@@ -1538,25 +1538,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.247482</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.220265</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>20.197903</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>7.043611</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>15.945841</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>9.454159000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.047497</v>
+        <v>7.418581</v>
       </c>
     </row>
     <row r="37">
@@ -1880,19 +1880,19 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>20.454269</v>
+        <v>0.256366</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>7.164379</v>
+        <v>0.120768</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>16.157392</v>
+        <v>0.211551</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>9.577635000000001</v>
+        <v>0.123476</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>7.575128</v>
+        <v>0.204044</v>
       </c>
     </row>
     <row r="49">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4957,7 +4957,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5965,7 +5969,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
@@ -12475,7 +12479,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -12522,7 +12526,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13918,7 +13922,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -13971,7 +13975,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">

--- a/output/pdf_financials_xlsx/BEEP.xlsx
+++ b/output/pdf_financials_xlsx/BEEP.xlsx
@@ -3416,16 +3416,16 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.72707</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.760024</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>-0.431354</v>
+        <v>-0.887565</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0.779773</v>
+        <v>1.351879</v>
       </c>
     </row>
     <row r="102">
@@ -3566,16 +3566,16 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.194471</v>
+        <v>-0.532599</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.020913</v>
+        <v>0.780937</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.689875</v>
+        <v>0.233664</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.382561</v>
+        <v>0.189545</v>
       </c>
     </row>
     <row r="107">
@@ -3716,13 +3716,13 @@
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.043611</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.210158</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -4426,13 +4426,13 @@
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.043611</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.210158</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-11.750714</v>
+        <v>-11.960872</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-7.683937</v>
@@ -4483,7 +4483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K220"/>
+  <dimension ref="A1:K224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5609,12 +5609,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Due from related parties 11</t>
+          <t>Amounts receivable 6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OtherPayable</t>
+          <t>AccountsReceivable</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -5627,19 +5627,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n">
-        <v>0.044104</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>0.068233</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>0.043271</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>0.431354</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5660,12 +5664,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Equipment 5</t>
+          <t>Due from related parties 11</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MachineryFurnitureEquipment</t>
+          <t>OtherPayable</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -5679,18 +5683,16 @@
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.204315</v>
+        <v>0.044104</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0.202702</v>
+        <v>0.068233</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.162162</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.043271</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>0.043536</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5711,12 +5713,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 11</t>
+          <t>Equipment 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
+          <t>MachineryFurnitureEquipment</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5729,21 +5731,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G25" s="5" t="n">
+        <v>0.204315</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>0.294878</v>
+        <v>0.202702</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0.431536</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.162162</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>0.318874</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -5764,10 +5762,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Flow-through share premium liability 9</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities 11 $</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -5783,16 +5785,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n">
-        <v>1.216117</v>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I26" s="5" t="n">
-        <v>2.663741</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.431536</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>1.464425</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5808,17 +5810,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Share capital 10</t>
+          <t>Due to related party</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
+          <t>OtherPayable</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5831,19 +5833,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G27" s="5" t="n">
-        <v>24.073364</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>26.776384</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>37.437349</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>0.0009940000000000001</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -5859,19 +5865,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reserves 10</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>AdditionalPaidInCapital</t>
-        </is>
-      </c>
+          <t>Flow-through share premium liability 9</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -5882,19 +5884,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n">
-        <v>6.175045</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>7.706056</v>
+        <v>1.216117</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>11.783804</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.663741</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>1.682573</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5910,17 +5912,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Share capital 10</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5934,20 +5936,16 @@
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.20656</v>
+        <v>24.073364</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.294878</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>26.776384</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>37.437349</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>40.308719</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5961,42 +5959,42 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SHAREHOLDERS’ EQUITY</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cash (note 4) $</t>
+          <t>Reserves 10</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CashAndCashEquivalents</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>0.247482</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>0.220265</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>6.175045</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>7.706056</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>11.783804</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>13.148157</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -6010,22 +6008,30 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SHAREHOLDERS’ EQUITY</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Total Assets $</t>
+          <t>TOTAL LIABILITIES AND SHAREHOLDERS’ EQUITY $</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TotalAssets</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0.247482</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>0.220265</v>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -6037,15 +6043,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="5" t="n">
+        <v>16.38491</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>10.84943</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -6059,10 +6061,14 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued Liabilities $</t>
+          <t>Accounts payable and accrued liabilities 11</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6070,26 +6076,26 @@
           <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
-      <c r="E32" s="5" t="n">
-        <v>0.010273</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>0.011859</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H32" s="5" t="n">
+        <v>0.294878</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0.431536</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -6110,34 +6116,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Share capital (note 5)</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0.281921</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>0.281921</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.20656</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0.294878</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -6161,26 +6167,22 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Shareholders’ Equity</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Contributed surplus (note 5)</t>
+          <t>Cash (note 4) $</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AdditionalPaidInCapital</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.046924</v>
+        <v>0.247482</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.046924</v>
+        <v>0.220265</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -6214,26 +6216,22 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Shareholders’ Equity</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Total Assets $</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>-0.091636</v>
+        <v>0.247482</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>-0.120439</v>
+        <v>0.220265</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -6267,26 +6265,22 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Shareholders’ Equity</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Total Shareholders’ Equity</t>
+          <t>Accounts payable and accrued Liabilities $</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>StockholdersEquity</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.237209</v>
+        <v>0.010273</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.208406</v>
+        <v>0.011859</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -6327,19 +6321,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Total Liabilities and Shareholders’ Equity $</t>
+          <t>Share capital (note 5)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.247482</v>
+        <v>0.281921</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.220265</v>
+        <v>0.281921</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6375,20 +6369,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Incorporation to</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>December 31, 2019 December</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Contributed surplus (note 5)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
-        <v>0.002018</v>
+        <v>0.046924</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.046924</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -6424,20 +6422,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bank fees $</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
-        <v>3e-05</v>
+        <v>-0.091636</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.000171</v>
+        <v>-0.120439</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6473,20 +6475,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dues and filings fees</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Total Shareholders’ Equity</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
-        <v>0.016279</v>
+        <v>0.237209</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.008751</v>
+        <v>0.208406</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -6522,22 +6528,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>General office costs</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Total Liabilities and Shareholders’ Equity $</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
-        <v>0.00104</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.247482</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.220265</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -6573,20 +6581,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Incorporation to</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>December 31, 2019 December</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" s="5" t="n">
-        <v>0.0406</v>
+        <v>0.002018</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.019881</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -6627,17 +6635,15 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Stock based payments (note 5)</t>
+          <t>Bank fees $</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" s="5" t="n">
-        <v>0.033687</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3e-05</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0.000171</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -6678,15 +6684,15 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Dues and filings fees</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" s="5" t="n">
-        <v>0.091636</v>
+        <v>0.016279</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.028803</v>
+        <v>0.008751</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -6727,15 +6733,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
+          <t>General office costs</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" s="5" t="n">
-        <v>-0.091636</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>-0.028803</v>
+        <v>0.00104</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -6771,20 +6779,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Basic and diluted $</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.0406</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.019881</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -6820,20 +6828,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Weighted average shares outstanding</t>
+          <t>Stock based payments (note 5)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" s="5" t="n">
-        <v>1.69403</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>2.5</v>
+        <v>0.033687</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -6869,22 +6879,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Share Capital</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Opening balance $</t>
+          <t>Expenses total</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E48" s="5" t="n">
+        <v>0.091636</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.281921</v>
+        <v>0.028803</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6920,26 +6928,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Share Capital</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of common shares</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>CommonStock</t>
-        </is>
-      </c>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" s="5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.091636</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>-0.028803</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6975,22 +6977,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Share Capital</t>
+          <t>Net loss per share</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
+          <t>Basic and diluted $</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" s="5" t="n">
-        <v>-0.054842</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5e-08</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -7026,22 +7026,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Share Capital</t>
+          <t>Net loss per share</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Value of agent warrants issued</t>
+          <t>Weighted average shares outstanding</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" s="5" t="n">
-        <v>-0.013237</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.69403</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>2.5</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -7082,12 +7080,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Balance, December 31 $</t>
+          <t>Opening balance $</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" s="5" t="n">
-        <v>0.281921</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F52" s="5" t="n">
         <v>0.281921</v>
@@ -7126,22 +7126,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
+          <t>Share Capital</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Opening balance $</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>0.046924</v>
+          <t>Proceeds from issuance of common shares</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CommonStock</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -7177,17 +7181,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
+          <t>Share Capital</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Stock based payments</t>
+          <t>Share issue costs</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" s="5" t="n">
-        <v>0.033687</v>
+        <v>-0.054842</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7228,17 +7232,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
+          <t>Share Capital</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Agent warrants</t>
+          <t>Value of agent warrants issued</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" s="5" t="n">
-        <v>0.013237</v>
+        <v>-0.013237</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7279,7 +7283,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
+          <t>Share Capital</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7289,10 +7293,10 @@
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" s="5" t="n">
-        <v>0.046924</v>
+        <v>0.281921</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.046924</v>
+        <v>0.281921</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -7328,7 +7332,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Contributed surplus</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7343,7 +7347,7 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>-0.091636</v>
+        <v>0.046924</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -7379,20 +7383,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Contributed surplus</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Net loss for the period</t>
+          <t>Stock based payments</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" s="5" t="n">
-        <v>-0.091636</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>-0.028803</v>
+        <v>0.033687</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7428,20 +7434,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Contributed surplus</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Balance, December 31 $</t>
+          <t>Agent warrants</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="n">
-        <v>-0.091636</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>-0.120439</v>
+        <v>0.013237</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7477,24 +7485,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Contributed surplus</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Total Shareholders’ Equity $</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
+          <t>Balance, December 31 $</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" s="5" t="n">
-        <v>0.237209</v>
+        <v>0.046924</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.208406</v>
+        <v>0.046924</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7528,24 +7532,24 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Deficit</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Accrued Liabilities $</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>CurrentAccruedExpenses</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>0.010273</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Opening balance $</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>-0.091636</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7581,22 +7585,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Share Capital (note</t>
+          <t>Net loss for the period</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" s="5" t="n">
-        <v>5e-06</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.091636</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>-0.028803</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7632,24 +7634,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Balance, January 30, 2018 $</t>
+          <t>Balance, December 31 $</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E63" s="5" t="n">
+        <v>-0.091636</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>-0.120439</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7685,26 +7683,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of common shares</t>
+          <t>Total Shareholders’ Equity $</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CommonStock</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.237209</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0.208406</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7738,19 +7734,19 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Net loss per share</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Accrued Liabilities $</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CurrentAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
-        <v>-0.054842</v>
+        <v>0.010273</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7796,12 +7792,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Value of agent warrants issued</t>
+          <t>Share Capital (note</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" s="5" t="n">
-        <v>-0.013237</v>
+        <v>5e-06</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7847,12 +7843,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2018 $</t>
+          <t>Balance, January 30, 2018 $</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" s="5" t="n">
-        <v>0.281921</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7898,12 +7896,16 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Contributed surplus (note</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Proceeds from issuance of common shares</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CommonStock</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="n">
-        <v>5e-06</v>
+        <v>0.35</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7949,12 +7951,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Stock based payments</t>
+          <t>Share issue costs</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" s="5" t="n">
-        <v>0.033687</v>
+        <v>-0.054842</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8000,12 +8002,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Agent warrants</t>
+          <t>Value of agent warrants issued</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" s="5" t="n">
-        <v>0.013237</v>
+        <v>-0.013237</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8046,19 +8048,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Net loss per share</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Balance, January 30, 2018 $</t>
+          <t>Balance, December 31, 2018 $</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E71" s="5" t="n">
+        <v>0.281921</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8099,17 +8099,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Net loss per share</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2018 $</t>
+          <t>Contributed surplus (note</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" s="5" t="n">
-        <v>-0.091636</v>
+        <v>5e-06</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8145,20 +8145,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Net loss per share</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>For the years ended December 31, 2025 December</t>
+          <t>Stock based payments</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E73" s="5" t="n">
+        <v>0.033687</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8180,38 +8182,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J73" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="K73" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Net loss per share</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>(Loss) for the year</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Agent warrants</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" s="5" t="n">
+        <v>0.013237</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8233,34 +8233,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J74" s="5" t="n">
-        <v>-9.823918000000001</v>
-      </c>
-      <c r="K74" s="5" t="n">
-        <v>-17.770769</v>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Balance, January 30, 2018 $</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -8276,40 +8276,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H75" s="5" t="n">
-        <v>0.045224</v>
-      </c>
-      <c r="I75" s="5" t="n">
-        <v>0.04054</v>
-      </c>
-      <c r="J75" s="5" t="n">
-        <v>0.053446</v>
-      </c>
-      <c r="K75" s="5" t="n">
-        <v>0.09130099999999999</v>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Flow-through share premium recovery</t>
+          <t>Balance, December 31, 2018 $</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E76" s="5" t="n">
+        <v>-0.091636</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8321,17 +8327,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H76" s="5" t="n">
-        <v>-0.042</v>
-      </c>
-      <c r="I76" s="5" t="n">
-        <v>-1.31917</v>
-      </c>
-      <c r="J76" s="5" t="n">
-        <v>-2.981168</v>
-      </c>
-      <c r="K76" s="5" t="n">
-        <v>-2.182619</v>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -8340,21 +8354,13 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Items not involving cash</t>
-        </is>
-      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>For the years ended December 31, 2025 December</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -8381,12 +8387,10 @@
         </is>
       </c>
       <c r="J77" s="5" t="n">
-        <v>0.7662679999999999</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002024</v>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="78">
@@ -8397,15 +8401,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Unrealized (gain) on marketable securities</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>(Loss) for the year</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -8431,13 +8439,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J78" s="5" t="n">
+        <v>-9.823918000000001</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>-0.004163</v>
+        <v>-17.770769</v>
       </c>
     </row>
     <row r="79">
@@ -8453,10 +8459,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Acquisition of Forum 5</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -8472,23 +8482,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H79" s="5" t="n">
+        <v>0.045224</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>0.04054</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>0.053446</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>11.829151</v>
+        <v>0.09130099999999999</v>
       </c>
     </row>
     <row r="80">
@@ -8504,7 +8508,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Asset retirement expense</t>
+          <t>Flow-through share premium recovery</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -8523,23 +8527,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H80" s="5" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>-1.31917</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>-2.981168</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>0.149</v>
+        <v>-2.182619</v>
       </c>
     </row>
     <row r="81">
@@ -8550,17 +8548,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Amounts receivable</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8589,10 +8587,12 @@
         </is>
       </c>
       <c r="J81" s="5" t="n">
-        <v>-0.431354</v>
-      </c>
-      <c r="K81" s="5" t="n">
-        <v>0.779773</v>
+        <v>0.7662679999999999</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -8603,19 +8603,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>Unrealized (gain) on marketable securities</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -8641,11 +8637,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J82" s="5" t="n">
-        <v>0.08834</v>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K82" s="5" t="n">
-        <v>0.427253</v>
+        <v>-0.004163</v>
       </c>
     </row>
     <row r="83">
@@ -8656,12 +8654,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GST/HST receivable</t>
+          <t>Acquisition of Forum 5</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -8680,17 +8678,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H83" s="5" t="n">
-        <v>-0.72707</v>
-      </c>
-      <c r="I83" s="5" t="n">
-        <v>0.760024</v>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>-0.456211</v>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K83" s="5" t="n">
-        <v>0.572106</v>
+        <v>11.829151</v>
       </c>
     </row>
     <row r="84">
@@ -8701,19 +8705,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Asset retirement expense</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -8729,17 +8729,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H84" s="5" t="n">
-        <v>0.034744</v>
-      </c>
-      <c r="I84" s="5" t="n">
-        <v>0.136658</v>
-      </c>
-      <c r="J84" s="5" t="n">
-        <v>1.032889</v>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-1.589587</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="85">
@@ -8755,10 +8761,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Related party</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Amounts receivable</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -8785,10 +8795,10 @@
         </is>
       </c>
       <c r="J85" s="5" t="n">
-        <v>0.0009940000000000001</v>
+        <v>-0.431354</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>0.014617</v>
+        <v>0.779773</v>
       </c>
     </row>
     <row r="86">
@@ -8804,12 +8814,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Net cash (used in) operating activities</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8838,10 +8848,10 @@
         </is>
       </c>
       <c r="J86" s="5" t="n">
-        <v>-11.750714</v>
+        <v>0.08834</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-7.683937</v>
+        <v>0.427253</v>
       </c>
     </row>
     <row r="87">
@@ -8852,15 +8862,19 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Proceeds from equity financings, net 9</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>GST/HST receivable</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -8876,21 +8890,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H87" s="5" t="n">
+        <v>-0.72707</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>0.760024</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>5.469455</v>
+        <v>-0.456211</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>5.567404</v>
+        <v>0.572106</v>
       </c>
     </row>
     <row r="88">
@@ -8901,17 +8911,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8930,16 +8940,16 @@
         </is>
       </c>
       <c r="H88" s="5" t="n">
-        <v>3.939546</v>
+        <v>0.034744</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>15.666967</v>
+        <v>0.136658</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>5.469455</v>
+        <v>1.032889</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>5.567404</v>
+        <v>-1.589587</v>
       </c>
     </row>
     <row r="89">
@@ -8950,12 +8960,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Purchase of equipment</t>
+          <t>Related party</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -8974,8 +8984,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H89" s="5" t="n">
-        <v>-0.043611</v>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -8983,12 +8995,10 @@
         </is>
       </c>
       <c r="J89" s="5" t="n">
-        <v>-0.210158</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0009940000000000001</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>0.014617</v>
       </c>
     </row>
     <row r="90">
@@ -8999,15 +9009,19 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cash obtained from Acquisition of Forum 5</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>Net cash (used in) operating activities</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -9033,13 +9047,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J90" s="5" t="n">
+        <v>-11.750714</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>0.033458</v>
+        <v>-7.683937</v>
       </c>
     </row>
     <row r="91">
@@ -9050,19 +9062,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Net cash provided by (used in) investing activities</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Proceeds from equity financings, net 9</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -9089,10 +9097,10 @@
         </is>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.210423</v>
+        <v>5.469455</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>0.033458</v>
+        <v>5.567404</v>
       </c>
     </row>
     <row r="92">
@@ -9103,17 +9111,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Net (decrease) in cash</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9131,21 +9139,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H92" s="5" t="n">
+        <v>3.939546</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>15.666967</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>-6.491682</v>
+        <v>5.469455</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-2.083075</v>
+        <v>5.567404</v>
       </c>
     </row>
     <row r="93">
@@ -9161,12 +9165,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Purchase of equipment</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>PurchaseOfPPE</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9185,16 +9189,20 @@
         </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>20.197903</v>
-      </c>
-      <c r="I93" s="5" t="n">
-        <v>7.043611</v>
+        <v>-0.043611</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J93" s="5" t="n">
-        <v>15.945841</v>
-      </c>
-      <c r="K93" s="5" t="n">
-        <v>9.454159000000001</v>
+        <v>-0.210158</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -9210,14 +9218,10 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Cash obtained from Acquisition of Forum 5</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -9233,17 +9237,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H94" s="5" t="n">
-        <v>7.043611</v>
-      </c>
-      <c r="I94" s="5" t="n">
-        <v>15.945841</v>
-      </c>
-      <c r="J94" s="5" t="n">
-        <v>9.454159000000001</v>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K94" s="5" t="n">
-        <v>7.371084</v>
+        <v>0.033458</v>
       </c>
     </row>
     <row r="95">
@@ -9254,15 +9264,19 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Supplement cash flow information</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Broker/finders warrants issued</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>Net cash provided by (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -9289,10 +9303,10 @@
         </is>
       </c>
       <c r="J95" s="5" t="n">
-        <v>0.095175</v>
+        <v>-0.210423</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>0.104856</v>
+        <v>0.033458</v>
       </c>
     </row>
     <row r="96">
@@ -9303,15 +9317,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>trading under the symbol “BEEP”.</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Directors of the Company on April</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Net (decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -9338,10 +9356,10 @@
         </is>
       </c>
       <c r="J96" s="5" t="n">
-        <v>0.002026</v>
+        <v>-6.491682</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>3e-05</v>
+        <v>-2.083075</v>
       </c>
     </row>
     <row r="97">
@@ -9352,15 +9370,19 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3.    MATERIAL ACCOUNTING POLICIES AND BASIS OF PREPARATION</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Accounting Standards Board (“IASB”) and interpretations of the International Financial Reporting Interpretations Committee (“IFRIC”). The policies applied in these financial statements are based on IFRS issued and effective as of December</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -9376,21 +9398,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H97" s="5" t="n">
+        <v>20.197903</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>7.043611</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>0.002025</v>
+        <v>15.945841</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>9.454159000000001</v>
       </c>
     </row>
     <row r="98">
@@ -9399,13 +9417,21 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>For the year ended December 31, 2024 December</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>Cash, end of year</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -9421,21 +9447,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H98" s="5" t="n">
+        <v>7.043611</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>0.002023</v>
+        <v>15.945841</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.454159000000001</v>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>7.371084</v>
       </c>
     </row>
     <row r="99">
@@ -9446,12 +9468,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Supplement cash flow information</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Flow-through share premium liability recovery</t>
+          <t>Broker/finders warrants issued</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -9475,16 +9497,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="5" t="n">
-        <v>-1.31917</v>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-2.981168</v>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.095175</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>0.104856</v>
       </c>
     </row>
     <row r="100">
@@ -9495,19 +9517,15 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>trading under the symbol “BEEP”.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Directors of the Company on April</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -9523,19 +9541,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H100" s="5" t="n">
-        <v>1.606176</v>
-      </c>
-      <c r="I100" s="5" t="n">
-        <v>1.83854</v>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J100" s="5" t="n">
-        <v>0.7662679999999999</v>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002026</v>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>3e-05</v>
       </c>
     </row>
     <row r="101">
@@ -9546,19 +9566,15 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>3.    MATERIAL ACCOUNTING POLICIES AND BASIS OF PREPARATION</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Prepaid expenses and deposits</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>Accounting Standards Board (“IASB”) and interpretations of the International Financial Reporting Interpretations Committee (“IFRIC”). The policies applied in these financial statements are based on IFRS issued and effective as of December</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -9574,19 +9590,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H101" s="5" t="n">
-        <v>0.159727</v>
-      </c>
-      <c r="I101" s="5" t="n">
-        <v>-0.115745</v>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J101" s="5" t="n">
-        <v>0.08834</v>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002025</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="102">
@@ -9595,14 +9613,10 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Due to related parties</t>
+          <t>For the year ended December 31, 2024 December</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -9627,10 +9641,10 @@
         </is>
       </c>
       <c r="I102" s="5" t="n">
-        <v>0.024962</v>
+        <v>0.002023</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>0.0009940000000000001</v>
+        <v>3.1e-05</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -9646,12 +9660,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Proceeds from equity financings, net</t>
+          <t>Flow-through share premium liability recovery</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -9670,14 +9684,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H103" s="5" t="n">
-        <v>2.754339</v>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I103" s="5" t="n">
-        <v>14.568795</v>
+        <v>-1.31917</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>5.469455</v>
+        <v>-2.981168</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -9693,15 +9709,19 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Proceeds from warrants exercised</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -9718,15 +9738,13 @@
         </is>
       </c>
       <c r="H104" s="5" t="n">
-        <v>1.050958</v>
+        <v>1.606176</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>1.090172</v>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.83854</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>0.7662679999999999</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -9742,17 +9760,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Proceeds from stock options exercised</t>
+          <t>Prepaid expenses and deposits</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ProceedsFromStockOptionExercised</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9771,15 +9789,13 @@
         </is>
       </c>
       <c r="H105" s="5" t="n">
-        <v>0.134249</v>
+        <v>0.159727</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.115745</v>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>0.08834</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -9795,12 +9811,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Advances to related parties</t>
+          <t>Due to related parties</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -9824,13 +9840,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I106" s="5" t="n">
+        <v>0.024962</v>
       </c>
       <c r="J106" s="5" t="n">
-        <v>-0.000265</v>
+        <v>0.0009940000000000001</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -9846,19 +9860,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Net (decrease)/increase in cash</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Proceeds from equity financings, net</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -9875,13 +9885,13 @@
         </is>
       </c>
       <c r="H107" s="5" t="n">
-        <v>-13.154292</v>
+        <v>2.754339</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>8.902229999999999</v>
+        <v>14.568795</v>
       </c>
       <c r="J107" s="5" t="n">
-        <v>-6.491682</v>
+        <v>5.469455</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -9897,12 +9907,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Supplement cash flow information</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Broker/finders warrants issued $</t>
+          <t>Proceeds from warrants exercised</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -9922,13 +9932,15 @@
         </is>
       </c>
       <c r="H108" s="5" t="n">
-        <v>0.041604</v>
+        <v>1.050958</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>0.315422</v>
-      </c>
-      <c r="J108" s="5" t="n">
-        <v>0.095175</v>
+        <v>1.090172</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -9944,15 +9956,19 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Due from related parties</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>Proceeds from stock options exercised</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ProceedsFromStockOptionExercised</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -9969,10 +9985,10 @@
         </is>
       </c>
       <c r="H109" s="5" t="n">
-        <v>-0.024129</v>
+        <v>0.134249</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>0.024962</v>
+        <v>0.008</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -9991,10 +10007,14 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>Advances to related parties</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -10013,18 +10033,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H110" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J110" s="5" t="n">
+        <v>-0.000265</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -10038,13 +10058,21 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>For the years ended</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>Net (decrease)/increase in cash</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -10061,17 +10089,13 @@
         </is>
       </c>
       <c r="H111" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-13.154292</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>8.902229999999999</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>-6.491682</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -10087,19 +10111,15 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Supplement cash flow information</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Amortization 45,224</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Broker/finders warrants issued $</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -10116,17 +10136,13 @@
         </is>
       </c>
       <c r="H112" s="5" t="n">
-        <v>0.041286</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.041604</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>0.315422</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>0.095175</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -10142,12 +10158,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Flow-through share premium recovery (42,000)</t>
+          <t>Due from related parties</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -10167,12 +10183,10 @@
         </is>
       </c>
       <c r="H113" s="5" t="n">
-        <v>-0.296454</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.024129</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>0.024962</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -10191,21 +10205,13 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Items not involving cash</t>
-        </is>
-      </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Share-based payments 1,606,176</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -10222,7 +10228,7 @@
         </is>
       </c>
       <c r="H114" s="5" t="n">
-        <v>2.411392</v>
+        <v>3.1e-05</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -10246,14 +10252,10 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Items not involving cash</t>
-        </is>
-      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Shares issued for consulting expenses -</t>
+          <t>For the years ended</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -10273,7 +10275,7 @@
         </is>
       </c>
       <c r="H115" s="5" t="n">
-        <v>0.118</v>
+        <v>0.002021</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -10299,17 +10301,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Prepaid expenses and deposits 159,727</t>
+          <t>Amortization 45,224</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10328,7 +10330,7 @@
         </is>
       </c>
       <c r="H116" s="5" t="n">
-        <v>-0.167572</v>
+        <v>0.041286</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -10354,12 +10356,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>GST/HST receivable (727,070)</t>
+          <t>Flow-through share premium recovery (42,000)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -10379,7 +10381,7 @@
         </is>
       </c>
       <c r="H117" s="5" t="n">
-        <v>-0.049052</v>
+        <v>-0.296454</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -10405,17 +10407,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 34,744</t>
+          <t>Share-based payments 1,606,176</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10434,7 +10436,7 @@
         </is>
       </c>
       <c r="H118" s="5" t="n">
-        <v>-0.07606599999999999</v>
+        <v>2.411392</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -10460,12 +10462,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Issue of common shares and warrants -</t>
+          <t>Shares issued for consulting expenses -</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -10485,7 +10487,7 @@
         </is>
       </c>
       <c r="H119" s="5" t="n">
-        <v>16.806801</v>
+        <v>0.118</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -10511,15 +10513,19 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Warrants exercised 1,050,958</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
+          <t>Prepaid expenses and deposits 159,727</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -10536,7 +10542,7 @@
         </is>
       </c>
       <c r="H120" s="5" t="n">
-        <v>3.224415</v>
+        <v>-0.167572</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -10562,19 +10568,15 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Share issue costs -</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>GST/HST receivable (727,070)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -10591,7 +10593,7 @@
         </is>
       </c>
       <c r="H121" s="5" t="n">
-        <v>-1.227733</v>
+        <v>-0.049052</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -10617,15 +10619,19 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Stock options exercised 134,249</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities 34,744</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -10642,7 +10648,7 @@
         </is>
       </c>
       <c r="H122" s="5" t="n">
-        <v>0.308</v>
+        <v>-0.07606599999999999</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -10673,7 +10679,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Shares issued on flow-through private placement, net 2,754,339</t>
+          <t>Issue of common shares and warrants -</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -10692,10 +10698,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H123" s="5" t="n">
+        <v>16.806801</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -10726,7 +10730,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities $3,939,546</t>
+          <t>Warrants exercised 1,050,958</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -10746,7 +10750,7 @@
         </is>
       </c>
       <c r="H124" s="5" t="n">
-        <v>19.111483</v>
+        <v>3.224415</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -10772,15 +10776,19 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Purchase of equipment (43,611)</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
+          <t>Share issue costs -</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -10797,7 +10805,7 @@
         </is>
       </c>
       <c r="H125" s="5" t="n">
-        <v>-0.124991</v>
+        <v>-1.227733</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -10823,12 +10831,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Due from related parties (24,129)</t>
+          <t>Stock options exercised 134,249</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -10848,7 +10856,7 @@
         </is>
       </c>
       <c r="H126" s="5" t="n">
-        <v>-0.017814</v>
+        <v>0.308</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -10874,12 +10882,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities                                       $(67,740)       $(142,805)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Net (decrease)/increase in cash (13,154,292)</t>
+          <t>Shares issued on flow-through private placement, net 2,754,339</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -10898,8 +10906,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H127" s="5" t="n">
-        <v>13.95788</v>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -10925,19 +10935,15 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities                                       $(67,740)       $(142,805)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cash, beginning of year 20,197,903</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Net cash provided by financing activities $3,939,546</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -10954,7 +10960,7 @@
         </is>
       </c>
       <c r="H128" s="5" t="n">
-        <v>6.240023</v>
+        <v>19.111483</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -10980,12 +10986,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities                                       $(67,740)       $(142,805)</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Cash, end of year $7,043,611</t>
+          <t>Purchase of equipment (43,611)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -11005,7 +11011,7 @@
         </is>
       </c>
       <c r="H129" s="5" t="n">
-        <v>20.197903</v>
+        <v>-0.124991</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -11031,12 +11037,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Supplement cash flow information</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Broker warrants issued $ 41,604 $</t>
+          <t>Due from related parties (24,129)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -11056,7 +11062,7 @@
         </is>
       </c>
       <c r="H130" s="5" t="n">
-        <v>0.398045</v>
+        <v>-0.017814</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -11082,30 +11088,32 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Incorporation to</t>
+          <t>Net cash used in investing activities                                       $(67,740)       $(142,805)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>December 31, 2019 December</t>
+          <t>Net (decrease)/increase in cash (13,154,292)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F131" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H131" s="5" t="n">
+        <v>13.95788</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -11131,34 +11139,36 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Net cash used in investing activities                                       $(67,740)       $(142,805)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Net loss $</t>
+          <t>Cash, beginning of year 20,197,903</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="n">
-        <v>-0.091636</v>
-      </c>
-      <c r="F132" s="5" t="n">
-        <v>-0.028803</v>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H132" s="5" t="n">
+        <v>6.240023</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -11184,17 +11194,19 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Net cash used in investing activities                                       $(67,740)       $(142,805)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Stock based payments</t>
+          <t>Cash, end of year $7,043,611</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
-      <c r="E133" s="5" t="n">
-        <v>0.033687</v>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11206,10 +11218,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H133" s="5" t="n">
+        <v>20.197903</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -11235,34 +11245,32 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Change in non-cash operating working capital</t>
+          <t>Supplement cash flow information</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="n">
-        <v>0.010273</v>
-      </c>
-      <c r="F134" s="5" t="n">
-        <v>0.001586</v>
+          <t>Broker warrants issued $ 41,604 $</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H134" s="5" t="n">
+        <v>0.398045</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -11288,24 +11296,20 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Change in non-cash operating working capital</t>
+          <t>Incorporation to</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>December 31, 2019 December</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" s="5" t="n">
-        <v>-0.047676</v>
+        <v>0.002018</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>-0.027217</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -11341,26 +11345,24 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of common shares</t>
+          <t>Net loss $</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.091636</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>-0.028803</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -11394,19 +11396,19 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Share issue costs (note 5)</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>Stock based payments</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" s="5" t="n">
-        <v>-0.054842</v>
+        <v>0.033687</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11445,24 +11447,26 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Change in non-cash operating working capital</t>
+        </is>
+      </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0.295158</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010273</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>0.001586</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -11496,19 +11500,23 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Change in non-cash operating working capital</t>
+        </is>
+      </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Increase in cash</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0.247482</v>
+        <v>-0.047676</v>
       </c>
       <c r="F139" s="5" t="n">
         <v>-0.027217</v>
@@ -11545,24 +11553,28 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
+          <t>Proceeds from issuance of common shares</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F140" s="5" t="n">
-        <v>0.247482</v>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -11599,19 +11611,21 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cash, end of period $</t>
+          <t>Share issue costs (note 5)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0.247482</v>
-      </c>
-      <c r="F141" s="5" t="n">
-        <v>0.220265</v>
+        <v>-0.054842</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -11645,23 +11659,19 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Change in non-cash operating working capital</t>
-        </is>
-      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Trade and other payables</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0.010273</v>
+        <v>0.295158</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11700,28 +11710,22 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Financing</t>
-        </is>
-      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of common shares (note 5)</t>
+          <t>Increase in cash</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.247482</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>-0.027217</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -11755,28 +11759,24 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Financing</t>
-        </is>
-      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Share issue costs (note 5)</t>
+          <t>Cash, beginning of period</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E144" s="5" t="n">
-        <v>-0.054842</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>0.247482</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -11810,28 +11810,22 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Financing</t>
-        </is>
-      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Cash, end of period $</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0.295158</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.247482</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>0.220265</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -11867,21 +11861,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Change in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Increase in cash</t>
+          <t>Trade and other payables</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0.247482</v>
+        <v>0.010273</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11927,18 +11921,16 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
+          <t>Proceeds from issuance of common shares (note 5)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>0.35</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11984,16 +11976,16 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cash, end of period $</t>
+          <t>Share issue costs (note 5)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0.247482</v>
+        <v>-0.054842</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12029,20 +12021,26 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>For the years ended Notes December 31, 2025 December</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>0.295158</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12064,34 +12062,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J149" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="K149" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures 7,12</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase in cash</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="n">
+        <v>0.247482</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12113,30 +12117,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J150" s="5" t="n">
-        <v>11.621055</v>
-      </c>
-      <c r="K150" s="5" t="n">
-        <v>18.850775</v>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder total</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>Cash, beginning of period</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -12147,43 +12159,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G151" s="5" t="n">
-        <v>0.363165</v>
-      </c>
-      <c r="H151" s="5" t="n">
-        <v>0.48083</v>
-      </c>
-      <c r="I151" s="5" t="n">
-        <v>0.435923</v>
-      </c>
-      <c r="J151" s="5" t="n">
-        <v>0.41625</v>
-      </c>
-      <c r="K151" s="5" t="n">
-        <v>0.295589</v>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>communications</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Management and consulting 12</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of period $</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="n">
+        <v>0.247482</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12205,11 +12229,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J152" s="5" t="n">
-        <v>0.357555</v>
-      </c>
-      <c r="K152" s="5" t="n">
-        <v>0.361392</v>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -12218,21 +12246,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>communications</t>
-        </is>
-      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>For the years ended Notes December 31, 2025 December</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -12243,20 +12263,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G153" s="5" t="n">
-        <v>0.09292400000000001</v>
-      </c>
-      <c r="H153" s="5" t="n">
-        <v>0.093574</v>
-      </c>
-      <c r="I153" s="5" t="n">
-        <v>0.101259</v>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J153" s="5" t="n">
-        <v>0.074909</v>
+        <v>0.002024</v>
       </c>
       <c r="K153" s="5" t="n">
-        <v>0.226659</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="154">
@@ -12267,12 +12293,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>communications</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Share-based compensation 11,12</t>
+          <t>Exploration and evaluation expenditures 7,12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -12302,12 +12328,10 @@
         </is>
       </c>
       <c r="J154" s="5" t="n">
-        <v>0.7662679999999999</v>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>11.621055</v>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>18.850775</v>
       </c>
     </row>
     <row r="155">
@@ -12318,19 +12342,15 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>communications</t>
+          <t>Transfer agent, filing fees and shareholder</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Office, general and administrative</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Transfer agent, filing fees and shareholder total</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -12342,19 +12362,19 @@
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.061279</v>
+        <v>0.363165</v>
       </c>
       <c r="H155" s="5" t="n">
-        <v>0.233629</v>
+        <v>0.48083</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>0.222562</v>
+        <v>0.435923</v>
       </c>
       <c r="J155" s="5" t="n">
-        <v>0.186923</v>
+        <v>0.41625</v>
       </c>
       <c r="K155" s="5" t="n">
-        <v>0.373958</v>
+        <v>0.295589</v>
       </c>
     </row>
     <row r="156">
@@ -12370,14 +12390,10 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Management and consulting 12</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -12404,10 +12420,10 @@
         </is>
       </c>
       <c r="J156" s="5" t="n">
-        <v>0.053446</v>
+        <v>0.357555</v>
       </c>
       <c r="K156" s="5" t="n">
-        <v>0.09130099999999999</v>
+        <v>0.361392</v>
       </c>
     </row>
     <row r="157">
@@ -12423,10 +12439,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Unrealized (gain) on marketable securities</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -12437,28 +12457,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G157" s="5" t="n">
+        <v>0.09292400000000001</v>
+      </c>
+      <c r="H157" s="5" t="n">
+        <v>0.093574</v>
+      </c>
+      <c r="I157" s="5" t="n">
+        <v>0.101259</v>
+      </c>
+      <c r="J157" s="5" t="n">
+        <v>0.074909</v>
       </c>
       <c r="K157" s="5" t="n">
-        <v>-0.004163</v>
+        <v>0.226659</v>
       </c>
     </row>
     <row r="158">
@@ -12474,14 +12486,10 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Share-based compensation 11,12</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -12492,20 +12500,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G158" s="5" t="n">
-        <v>-0.029203</v>
-      </c>
-      <c r="H158" s="5" t="n">
-        <v>-0.151278</v>
-      </c>
-      <c r="I158" s="5" t="n">
-        <v>-0.43908</v>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J158" s="5" t="n">
-        <v>-0.67132</v>
-      </c>
-      <c r="K158" s="5" t="n">
-        <v>-0.242123</v>
+        <v>0.7662679999999999</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -12521,12 +12537,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>TOTAL EXPENSES</t>
+          <t>Office, general and administrative</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -12540,19 +12556,19 @@
         </is>
       </c>
       <c r="G159" s="5" t="n">
-        <v>7.288786</v>
+        <v>0.061279</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>18.144899</v>
+        <v>0.233629</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>9.449716</v>
+        <v>0.222562</v>
       </c>
       <c r="J159" s="5" t="n">
-        <v>12.805086</v>
+        <v>0.186923</v>
       </c>
       <c r="K159" s="5" t="n">
-        <v>19.953388</v>
+        <v>0.373958</v>
       </c>
     </row>
     <row r="160">
@@ -12568,10 +12584,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Net (Loss) before tax for the year</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -12598,10 +12618,10 @@
         </is>
       </c>
       <c r="J160" s="5" t="n">
-        <v>-12.805086</v>
+        <v>0.053446</v>
       </c>
       <c r="K160" s="5" t="n">
-        <v>-19.953388</v>
+        <v>0.09130099999999999</v>
       </c>
     </row>
     <row r="161">
@@ -12617,7 +12637,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Flow-through share premium liability recovery 8</t>
+          <t>Unrealized (gain) on marketable securities</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -12646,11 +12666,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J161" s="5" t="n">
-        <v>-2.981168</v>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K161" s="5" t="n">
-        <v>-2.182619</v>
+        <v>-0.004163</v>
       </c>
     </row>
     <row r="162">
@@ -12661,15 +12683,19 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NET (LOSS) AND COMPREHENSIVE LOSS</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>FOR THE YEAR</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -12680,26 +12706,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G162" s="5" t="n">
+        <v>-0.029203</v>
+      </c>
+      <c r="H162" s="5" t="n">
+        <v>-0.151278</v>
+      </c>
+      <c r="I162" s="5" t="n">
+        <v>-0.43908</v>
       </c>
       <c r="J162" s="5" t="n">
-        <v>-9.823918000000001</v>
+        <v>-0.67132</v>
       </c>
       <c r="K162" s="5" t="n">
-        <v>-17.770769</v>
+        <v>-0.242123</v>
       </c>
     </row>
     <row r="163">
@@ -12710,15 +12730,19 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Weighted average number of shares - basic</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Weighted average number of shares - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -12729,26 +12753,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G163" s="5" t="n">
+        <v>7.288786</v>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>18.144899</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>9.449716</v>
       </c>
       <c r="J163" s="5" t="n">
-        <v>26.727964</v>
+        <v>12.805086</v>
       </c>
       <c r="K163" s="5" t="n">
-        <v>37.83081</v>
+        <v>19.953388</v>
       </c>
     </row>
     <row r="164">
@@ -12759,19 +12777,15 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Weighted average number of shares - basic</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>(Loss) per share – basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Net (Loss) before tax for the year</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -12798,10 +12812,10 @@
         </is>
       </c>
       <c r="J164" s="5" t="n">
-        <v>-3.7e-07</v>
+        <v>-12.805086</v>
       </c>
       <c r="K164" s="5" t="n">
-        <v>-4.699999999999999e-07</v>
+        <v>-19.953388</v>
       </c>
     </row>
     <row r="165">
@@ -12810,10 +12824,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>communications</t>
+        </is>
+      </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>For the years ended Notes December 31, 2024 December</t>
+          <t>Flow-through share premium liability recovery 8</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -12837,16 +12855,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I165" s="5" t="n">
-        <v>0.002023</v>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J165" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.981168</v>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>-2.182619</v>
       </c>
     </row>
     <row r="166">
@@ -12857,12 +12875,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>NET (LOSS) AND COMPREHENSIVE LOSS</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures 6,11</t>
+          <t>FOR THE YEAR</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -12876,22 +12894,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G166" s="5" t="n">
-        <v>3.947421</v>
-      </c>
-      <c r="H166" s="5" t="n">
-        <v>15.430554</v>
-      </c>
-      <c r="I166" s="5" t="n">
-        <v>6.794936</v>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J166" s="5" t="n">
-        <v>11.621055</v>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9.823918000000001</v>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>-17.770769</v>
       </c>
     </row>
     <row r="167">
@@ -12902,12 +12924,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Weighted average number of shares - basic</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Share-based compensation 10, 11</t>
+          <t>Weighted average number of shares - basic and diluted</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -12931,16 +12953,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I167" s="5" t="n">
-        <v>1.83854</v>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J167" s="5" t="n">
-        <v>0.7662679999999999</v>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>26.727964</v>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>37.83081</v>
       </c>
     </row>
     <row r="168">
@@ -12951,15 +12973,19 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Weighted average number of shares - basic</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Management and consulting 11</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
+          <t>(Loss) per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -12970,22 +12996,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G168" s="5" t="n">
-        <v>0.400522</v>
-      </c>
-      <c r="H168" s="5" t="n">
-        <v>0.40619</v>
-      </c>
-      <c r="I168" s="5" t="n">
-        <v>0.455036</v>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J168" s="5" t="n">
-        <v>0.357555</v>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.7e-07</v>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>-4.699999999999999e-07</v>
       </c>
     </row>
     <row r="169">
@@ -12994,21 +13024,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>communications</t>
-        </is>
-      </c>
+      <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Amortization 5</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>For the years ended Notes December 31, 2024 December</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -13019,17 +13041,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G169" s="5" t="n">
-        <v>0.041286</v>
-      </c>
-      <c r="H169" s="5" t="n">
-        <v>0.045224</v>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I169" s="5" t="n">
-        <v>0.04054</v>
+        <v>0.002023</v>
       </c>
       <c r="J169" s="5" t="n">
-        <v>0.053446</v>
+        <v>3.1e-05</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -13045,12 +13071,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>communications</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Loss for the year before tax</t>
+          <t>Exploration and evaluation expenditures 6,11</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -13064,21 +13090,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G170" s="5" t="n">
+        <v>3.947421</v>
+      </c>
+      <c r="H170" s="5" t="n">
+        <v>15.430554</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>-9.449716</v>
+        <v>6.794936</v>
       </c>
       <c r="J170" s="5" t="n">
-        <v>-12.805086</v>
+        <v>11.621055</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -13094,12 +13116,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Flow-through share premium liability recovery 9</t>
+          <t>Share-based compensation 10, 11</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -13124,10 +13146,10 @@
         </is>
       </c>
       <c r="I171" s="5" t="n">
-        <v>1.31917</v>
+        <v>1.83854</v>
       </c>
       <c r="J171" s="5" t="n">
-        <v>2.981168</v>
+        <v>0.7662679999999999</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -13143,19 +13165,15 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Weighted average number of shares - basic</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Weighted average number of shares - basic total</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Management and consulting 11</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -13166,21 +13184,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G172" s="5" t="n">
+        <v>0.400522</v>
+      </c>
+      <c r="H172" s="5" t="n">
+        <v>0.40619</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>97.478047</v>
+        <v>0.455036</v>
       </c>
       <c r="J172" s="5" t="n">
-        <v>132.420822</v>
+        <v>0.357555</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -13196,17 +13210,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>and diluted</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted</t>
+          <t>Amortization 5</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -13219,21 +13233,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G173" s="5" t="n">
+        <v>0.041286</v>
+      </c>
+      <c r="H173" s="5" t="n">
+        <v>0.045224</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>8e-08</v>
+        <v>0.04054</v>
       </c>
       <c r="J173" s="5" t="n">
-        <v>7e-08</v>
+        <v>0.053446</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -13249,19 +13259,15 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>of shares                       Reserve</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss for the year before tax</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -13283,10 +13289,10 @@
         </is>
       </c>
       <c r="I174" s="5" t="n">
-        <v>-8.130546000000001</v>
+        <v>-9.449716</v>
       </c>
       <c r="J174" s="5" t="n">
-        <v>-8.130546000000001</v>
+        <v>-12.805086</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -13302,12 +13308,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Shares issued on flow-through private</t>
+          <t>Deferred income tax recovery</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Shares issued on flow-through private</t>
+          <t>Flow-through share premium liability recovery 9</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -13332,12 +13338,10 @@
         </is>
       </c>
       <c r="I175" s="5" t="n">
-        <v>10.298074</v>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.31917</v>
+      </c>
+      <c r="J175" s="5" t="n">
+        <v>2.981168</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -13353,15 +13357,19 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Shares issued on hard-dollar private</t>
+          <t>Weighted average number of shares - basic</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Shares issued on hard-dollar private</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>Weighted average number of shares - basic total</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -13383,12 +13391,10 @@
         </is>
       </c>
       <c r="I176" s="5" t="n">
-        <v>1.503927</v>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>97.478047</v>
+      </c>
+      <c r="J176" s="5" t="n">
+        <v>132.420822</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -13404,15 +13410,19 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>placement</t>
+          <t>and diluted</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Stock options exercised 80,000 8,000 -</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>Loss per share – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -13434,12 +13444,10 @@
         </is>
       </c>
       <c r="I177" s="5" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8e-08</v>
+      </c>
+      <c r="J177" s="5" t="n">
+        <v>7e-08</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -13455,15 +13463,19 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>placement</t>
+          <t>of shares                       Reserve</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Warrants exercised 2,725,429 1,294,580 (204,408)</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+          <t>Net loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -13485,12 +13497,10 @@
         </is>
       </c>
       <c r="I178" s="5" t="n">
-        <v>1.090172</v>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.130546000000001</v>
+      </c>
+      <c r="J178" s="5" t="n">
+        <v>-8.130546000000001</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -13506,12 +13516,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>placement</t>
+          <t>Shares issued on flow-through private</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Share-based payments - - 1,838,540</t>
+          <t>Shares issued on flow-through private</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -13536,7 +13546,7 @@
         </is>
       </c>
       <c r="I179" s="5" t="n">
-        <v>1.83854</v>
+        <v>10.298074</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -13557,19 +13567,15 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>placement</t>
+          <t>Shares issued on hard-dollar private</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Shares issued on hard-dollar private</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -13591,10 +13597,12 @@
         </is>
       </c>
       <c r="I180" s="5" t="n">
-        <v>-9.823918000000001</v>
-      </c>
-      <c r="J180" s="5" t="n">
-        <v>-9.823918000000001</v>
+        <v>1.503927</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -13615,7 +13623,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Share-based payments - - 766,268</t>
+          <t>Stock options exercised 80,000 8,000 -</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -13640,7 +13648,7 @@
         </is>
       </c>
       <c r="I181" s="5" t="n">
-        <v>0.7662679999999999</v>
+        <v>0.008</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -13659,10 +13667,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>placement</t>
+        </is>
+      </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>For the years ended Notes December 31, 2023 December</t>
+          <t>Warrants exercised 2,725,429 1,294,580 (204,408)</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -13681,11 +13693,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H182" s="5" t="n">
-        <v>0.002022</v>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I182" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>1.090172</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -13706,12 +13720,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>placement</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Share-based compensation 11</t>
+          <t>Share-based payments - - 1,838,540</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -13725,11 +13739,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G183" s="5" t="n">
-        <v>2.411392</v>
-      </c>
-      <c r="H183" s="5" t="n">
-        <v>1.606176</v>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I183" s="5" t="n">
         <v>1.83854</v>
@@ -13753,17 +13771,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>placement</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Net loss for the year - - -</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -13781,16 +13799,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H184" s="5" t="n">
-        <v>0.093574</v>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I184" s="5" t="n">
-        <v>0.101259</v>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9.823918000000001</v>
+      </c>
+      <c r="J184" s="5" t="n">
+        <v>-9.823918000000001</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -13806,19 +13824,15 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>placement</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Office, general and administrative</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Share-based payments - - 766,268</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -13834,11 +13848,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H185" s="5" t="n">
-        <v>0.233629</v>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I185" s="5" t="n">
-        <v>0.222562</v>
+        <v>0.7662679999999999</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -13857,21 +13873,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
+      <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Amortization 5</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>For the years ended Notes December 31, 2023 December</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -13888,10 +13896,10 @@
         </is>
       </c>
       <c r="H186" s="5" t="n">
-        <v>0.045224</v>
+        <v>0.002022</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>0.04054</v>
+        <v>3.1e-05</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -13917,14 +13925,10 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Share-based compensation 11</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -13935,16 +13939,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G187" s="5" t="n">
+        <v>2.411392</v>
       </c>
       <c r="H187" s="5" t="n">
-        <v>-0.151278</v>
+        <v>1.606176</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>-0.43908</v>
+        <v>1.83854</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -13970,12 +13972,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>TOTAL EXPENSES</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -13994,10 +13996,10 @@
         </is>
       </c>
       <c r="H188" s="5" t="n">
-        <v>18.144899</v>
+        <v>0.093574</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>9.449716</v>
+        <v>0.101259</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -14023,12 +14025,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
+          <t>Office, general and administrative</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -14047,10 +14049,10 @@
         </is>
       </c>
       <c r="H189" s="5" t="n">
-        <v>-18.144899</v>
+        <v>0.233629</v>
       </c>
       <c r="I189" s="5" t="n">
-        <v>-9.449716</v>
+        <v>0.222562</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -14071,15 +14073,19 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Flow-through share premium recovery 9</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
+          <t>Amortization 5</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -14090,14 +14096,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G190" s="5" t="n">
-        <v>0.296454</v>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H190" s="5" t="n">
-        <v>-0.042</v>
+        <v>0.045224</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>-1.31917</v>
+        <v>0.04054</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -14118,17 +14126,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>NET LOSS FOR THE YEAR</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -14141,14 +14149,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G191" s="5" t="n">
-        <v>-6.992332</v>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H191" s="5" t="n">
-        <v>-18.102899</v>
+        <v>-0.151278</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>-8.130546000000001</v>
+        <v>-0.43908</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -14169,17 +14179,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted</t>
+          <t>TOTAL EXPENSES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -14198,10 +14208,10 @@
         </is>
       </c>
       <c r="H192" s="5" t="n">
-        <v>2.1e-07</v>
+        <v>18.144899</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>8e-08</v>
+        <v>9.449716</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -14222,15 +14232,19 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (18,102,899)</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -14247,10 +14261,10 @@
         </is>
       </c>
       <c r="H193" s="5" t="n">
-        <v>0.102899</v>
+        <v>-18.144899</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>1.8e-05</v>
+        <v>-9.449716</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -14276,7 +14290,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Stock options exercised 225,000 229,684 (95,435)</t>
+          <t>Flow-through share premium recovery 9</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -14290,18 +14304,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G194" s="5" t="n">
+        <v>0.296454</v>
       </c>
       <c r="H194" s="5" t="n">
-        <v>0.134249</v>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.042</v>
+      </c>
+      <c r="I194" s="5" t="n">
+        <v>-1.31917</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -14327,10 +14337,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Warrants exercised 2,773,954 1,281,208 (230,250)</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
+          <t>NET LOSS FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -14341,18 +14355,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G195" s="5" t="n">
+        <v>-6.992332</v>
       </c>
       <c r="H195" s="5" t="n">
-        <v>1.050958</v>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-18.102899</v>
+      </c>
+      <c r="I195" s="5" t="n">
+        <v>-8.130546000000001</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -14378,10 +14388,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Flow-through private placement, net 3,571,429 1,192,128 250,520</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>Loss per share – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -14398,12 +14412,10 @@
         </is>
       </c>
       <c r="H196" s="5" t="n">
-        <v>1.442648</v>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.1e-07</v>
+      </c>
+      <c r="I196" s="5" t="n">
+        <v>8e-08</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -14429,7 +14441,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Share-based payments - - 1,606,176</t>
+          <t>Loss for the year - - - (18,102,899)</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -14449,12 +14461,10 @@
         </is>
       </c>
       <c r="H197" s="5" t="n">
-        <v>1.606176</v>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.102899</v>
+      </c>
+      <c r="I197" s="5" t="n">
+        <v>1.8e-05</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -14480,14 +14490,10 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Stock options exercised 225,000 229,684 (95,435)</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -14504,10 +14510,12 @@
         </is>
       </c>
       <c r="H198" s="5" t="n">
-        <v>-8.130546000000001</v>
-      </c>
-      <c r="I198" s="5" t="n">
-        <v>-8.130546000000001</v>
+        <v>0.134249</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -14533,7 +14541,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Stock options exercised 80,000 8,000 -</t>
+          <t>Warrants exercised 2,773,954 1,281,208 (230,250)</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -14553,7 +14561,7 @@
         </is>
       </c>
       <c r="H199" s="5" t="n">
-        <v>0.008</v>
+        <v>1.050958</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -14584,7 +14592,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Warrants exercised 2,725,429 1,294,580 (204,408)</t>
+          <t>Flow-through private placement, net 3,571,429 1,192,128 250,520</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -14604,7 +14612,7 @@
         </is>
       </c>
       <c r="H200" s="5" t="n">
-        <v>1.090172</v>
+        <v>1.442648</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -14635,7 +14643,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Share-based payments - - 1,838,540</t>
+          <t>Share-based payments - - 1,606,176</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -14655,7 +14663,7 @@
         </is>
       </c>
       <c r="H201" s="5" t="n">
-        <v>1.83854</v>
+        <v>1.606176</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -14679,13 +14687,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Deferred income tax recovery</t>
+        </is>
+      </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>For the years ended Notes December 31, 2022 December</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -14696,16 +14712,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G202" s="5" t="n">
-        <v>0.002021</v>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H202" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.130546000000001</v>
+      </c>
+      <c r="I202" s="5" t="n">
+        <v>-8.130546000000001</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -14726,19 +14742,15 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>communications</t>
+          <t>Deferred income tax recovery</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Stock options exercised 80,000 8,000 -</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -14749,11 +14761,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G203" s="5" t="n">
-        <v>-7.288786</v>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H203" s="5" t="n">
-        <v>-18.144899</v>
+        <v>0.008</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -14779,12 +14793,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Weighted average number of shares -</t>
+          <t>Deferred income tax recovery</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Weighted average number of shares - total</t>
+          <t>Warrants exercised 2,725,429 1,294,580 (204,408)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -14798,11 +14812,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G204" s="5" t="n">
-        <v>58.973643</v>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H204" s="5" t="n">
-        <v>85.66572600000001</v>
+        <v>1.090172</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -14828,19 +14844,15 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>basic and diluted</t>
+          <t>Deferred income tax recovery</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Share-based payments - - 1,838,540</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -14851,11 +14863,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G205" s="5" t="n">
-        <v>1.2e-07</v>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H205" s="5" t="n">
-        <v>2.1e-07</v>
+        <v>1.83854</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -14879,21 +14893,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>of shares                       Reserve</t>
-        </is>
-      </c>
+      <c r="B206" t="inlineStr"/>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>For the years ended Notes December 31, 2022 December</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -14905,10 +14911,10 @@
         </is>
       </c>
       <c r="G206" s="5" t="n">
-        <v>-6.992332</v>
+        <v>0.002021</v>
       </c>
       <c r="H206" s="5" t="n">
-        <v>-6.992332</v>
+        <v>3.1e-05</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -14934,15 +14940,19 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>of shares                       Reserve</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Flow-through private placement 13,297,499 5,193,800 1,189,000</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -14954,12 +14964,10 @@
         </is>
       </c>
       <c r="G207" s="5" t="n">
-        <v>6.3828</v>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7.288786</v>
+      </c>
+      <c r="H207" s="5" t="n">
+        <v>-18.144899</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -14985,12 +14993,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>of shares                       Reserve</t>
+          <t>Weighted average number of shares -</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Hard-dollar private placement 10,549,234 8,527,001 1,897,000</t>
+          <t>Weighted average number of shares - total</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -15005,12 +15013,10 @@
         </is>
       </c>
       <c r="G208" s="5" t="n">
-        <v>10.424001</v>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>58.973643</v>
+      </c>
+      <c r="H208" s="5" t="n">
+        <v>85.66572600000001</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -15036,15 +15042,19 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>of shares                       Reserve</t>
+          <t>basic and diluted</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Shares issued for consulting expense 200,000 118,000 -</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
+          <t>Loss per share – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -15056,12 +15066,10 @@
         </is>
       </c>
       <c r="G209" s="5" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.2e-07</v>
+      </c>
+      <c r="H209" s="5" t="n">
+        <v>2.1e-07</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -15092,10 +15100,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Finder’s warrant issued - - 398,045</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -15107,12 +15119,10 @@
         </is>
       </c>
       <c r="G210" s="5" t="n">
-        <v>0.398045</v>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.992332</v>
+      </c>
+      <c r="H210" s="5" t="n">
+        <v>-6.992332</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -15143,7 +15153,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Shares issuance costs - (1,347,555) (278,223)</t>
+          <t>Flow-through private placement 13,297,499 5,193,800 1,189,000</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -15158,7 +15168,7 @@
         </is>
       </c>
       <c r="G211" s="5" t="n">
-        <v>-1.625778</v>
+        <v>6.3828</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -15194,7 +15204,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Stock options exercised 1,125,000 522,071 (214,071)</t>
+          <t>Hard-dollar private placement 10,549,234 8,527,001 1,897,000</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -15209,7 +15219,7 @@
         </is>
       </c>
       <c r="G212" s="5" t="n">
-        <v>0.308</v>
+        <v>10.424001</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -15245,7 +15255,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Warrants exercised 8,211,324 3,925,554 (701,139)</t>
+          <t>Shares issued for consulting expense 200,000 118,000 -</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -15260,7 +15270,7 @@
         </is>
       </c>
       <c r="G213" s="5" t="n">
-        <v>3.224415</v>
+        <v>0.118</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -15296,7 +15306,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 2,411,392</t>
+          <t>Finder’s warrant issued - - 398,045</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -15311,7 +15321,7 @@
         </is>
       </c>
       <c r="G214" s="5" t="n">
-        <v>2.411392</v>
+        <v>0.398045</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -15347,7 +15357,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (18,102,899)</t>
+          <t>Shares issuance costs - (1,347,555) (278,223)</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -15362,10 +15372,12 @@
         </is>
       </c>
       <c r="G215" s="5" t="n">
-        <v>0.102899</v>
-      </c>
-      <c r="H215" s="5" t="n">
-        <v>1.8e-05</v>
+        <v>-1.625778</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -15396,7 +15408,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Stock options exercised 225,000 229,684 (95,435)</t>
+          <t>Stock options exercised 1,125,000 522,071 (214,071)</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -15411,7 +15423,7 @@
         </is>
       </c>
       <c r="G216" s="5" t="n">
-        <v>0.134249</v>
+        <v>0.308</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -15447,7 +15459,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Warrants exercised 2,773,954 1,281,208 (230,250)</t>
+          <t>Warrants exercised 8,211,324 3,925,554 (701,139)</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -15462,7 +15474,7 @@
         </is>
       </c>
       <c r="G217" s="5" t="n">
-        <v>1.050958</v>
+        <v>3.224415</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -15498,7 +15510,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Flow-through private placement, net 3,571,429 1,192,128 250,520</t>
+          <t>Share-based compensation - - 2,411,392</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -15513,7 +15525,7 @@
         </is>
       </c>
       <c r="G218" s="5" t="n">
-        <v>1.442648</v>
+        <v>2.411392</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -15549,7 +15561,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Share-based payments - - 1,606,176</t>
+          <t>Loss for the year - - - (18,102,899)</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -15564,12 +15576,10 @@
         </is>
       </c>
       <c r="G219" s="5" t="n">
-        <v>1.606176</v>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.102899</v>
+      </c>
+      <c r="H219" s="5" t="n">
+        <v>1.8e-05</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -15600,7 +15610,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2022 90,204,249 $ 26,776,384 $7,706,056 $</t>
+          <t>Stock options exercised 225,000 229,684 (95,435)</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -15615,22 +15625,226 @@
         </is>
       </c>
       <c r="G220" s="5" t="n">
+        <v>0.134249</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>of shares                       Reserve</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Warrants exercised 2,773,954 1,281,208 (230,250)</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G221" s="5" t="n">
+        <v>1.050958</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>of shares                       Reserve</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Flow-through private placement, net 3,571,429 1,192,128 250,520</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G222" s="5" t="n">
+        <v>1.442648</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>of shares                       Reserve</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Share-based payments - - 1,606,176</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="n">
+        <v>1.606176</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>of shares                       Reserve</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Balance at December 31, 2022 90,204,249 $ 26,776,384 $7,706,056 $</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G224" s="5" t="n">
         <v>6.681466</v>
       </c>
-      <c r="H220" s="5" t="n">
+      <c r="H224" s="5" t="n">
         <v>-27.800974</v>
       </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
         <is>
           <t>-</t>
         </is>
